--- a/artfynd/A 11330-2025 artfynd.xlsx
+++ b/artfynd/A 11330-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186094</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>136186091</v>
       </c>
       <c r="B3" t="n">
-        <v>57311</v>
+        <v>57313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136186102</v>
       </c>
       <c r="B6" t="n">
-        <v>58262</v>
+        <v>58264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>136186109</v>
       </c>
       <c r="B7" t="n">
-        <v>58550</v>
+        <v>58552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136186101</v>
       </c>
       <c r="B9" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>136186112</v>
       </c>
       <c r="B10" t="n">
-        <v>58627</v>
+        <v>58629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>136186115</v>
       </c>
       <c r="B11" t="n">
-        <v>58729</v>
+        <v>58731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
